--- a/clustering_results/cost/01_Indoor_B1_LOS_Single_Results.xlsx
+++ b/clustering_results/cost/01_Indoor_B1_LOS_Single_Results.xlsx
@@ -458,10 +458,10 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -469,10 +469,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -491,10 +491,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -502,10 +502,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -513,10 +513,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -524,10 +524,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -535,10 +535,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -546,10 +546,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -557,10 +557,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -568,10 +568,10 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -579,10 +579,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -590,10 +590,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -601,10 +601,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -612,10 +612,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -626,7 +626,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -637,7 +637,7 @@
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -659,7 +659,7 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -670,7 +670,7 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -681,7 +681,7 @@
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -689,10 +689,10 @@
         <v>7</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -703,7 +703,7 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -711,10 +711,10 @@
         <v>7</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -722,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -733,7 +733,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -828,28 +828,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.877162376184962</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.5486111111111112</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7465312888655388</v>
+        <v>0.7698838581548467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3718487394957983</v>
+        <v>0.4182648401826484</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2692307692307693</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="J3" t="n">
         <v>9</v>
@@ -858,16 +858,16 @@
         <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0:01:33</t>
+          <t>0:07:27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[2.252723455429077, 2.2521350383758545, 2.251563787460327, 2.2510056495666504, 2.2504594326019287]</t>
+          <t>[1.9788358211517334, 1.917553186416626, 1.8315855264663696, 1.7707164287567139, 1.738787293434143, 1.7238504886627197, 1.7117133140563965, 1.699246883392334, 1.687751293182373, 1.6789182424545288, 1.6733109951019287, 1.6692109107971191, 1.6643205881118774, 1.6585500240325928, 1.654581904411316, 1.6543859243392944, 1.653117299079895, 1.649268627166748, 1.646502137184143, 1.6458358764648438, 1.6454607248306274, 1.6441702842712402, 1.6418348550796509, 1.639269471168518, 1.637896180152893, 1.6368778944015503, 1.6358642578125, 1.6351113319396973, 1.6335599422454834, 1.6330205202102661, 1.6312638521194458, 1.6313306093215942, 1.6314092874526978, 1.6308544874191284, 1.6308057308197021, 1.6307196617126465, 1.6303220987319946, 1.629219651222229, 1.62966787815094, 1.628572702407837]</t>
         </is>
       </c>
     </row>
